--- a/output/stock_quant_scores/AAPL_info.xlsx
+++ b/output/stock_quant_scores/AAPL_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FW2"/>
+  <dimension ref="A1:GA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1086,235 +1086,255 @@
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FU1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1440,28 +1460,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>254.43</v>
+        <v>256.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>255.22</v>
+        <v>254.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>251.04</v>
+        <v>253.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>255.73</v>
+        <v>257.36</v>
       </c>
       <c r="AG2" t="n">
-        <v>254.43</v>
+        <v>256.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>255.22</v>
+        <v>254.13</v>
       </c>
       <c r="AI2" t="n">
-        <v>251.04</v>
+        <v>253.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>255.73</v>
+        <v>257.36</v>
       </c>
       <c r="AK2" t="n">
         <v>1.04</v>
@@ -1482,40 +1502,40 @@
         <v>1.109</v>
       </c>
       <c r="AQ2" t="n">
-        <v>38.17754</v>
+        <v>38.764793</v>
       </c>
       <c r="AR2" t="n">
-        <v>30.27557</v>
+        <v>30.741274</v>
       </c>
       <c r="AS2" t="n">
-        <v>24408679</v>
+        <v>45566241</v>
       </c>
       <c r="AT2" t="n">
-        <v>24408679</v>
+        <v>45566241</v>
       </c>
       <c r="AU2" t="n">
-        <v>57103496</v>
+        <v>56787322</v>
       </c>
       <c r="AV2" t="n">
-        <v>71584280</v>
+        <v>66996360</v>
       </c>
       <c r="AW2" t="n">
-        <v>71584280</v>
+        <v>66996360</v>
       </c>
       <c r="AX2" t="n">
-        <v>250.96</v>
+        <v>241.21</v>
       </c>
       <c r="AY2" t="n">
-        <v>256.97</v>
+        <v>266.97</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>3733693661184</v>
+        <v>3791126003712</v>
       </c>
       <c r="BC2" t="n">
         <v>169.21</v>
@@ -1530,19 +1550,19 @@
         <v>0.049107</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.137214</v>
+        <v>9.277763</v>
       </c>
       <c r="BH2" t="n">
-        <v>225.7436</v>
+        <v>228.4506</v>
       </c>
       <c r="BI2" t="n">
-        <v>221.79485</v>
+        <v>221.9736</v>
       </c>
       <c r="BJ2" t="n">
         <v>1.01</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0039696577</v>
+        <v>0.00393195</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1553,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>3822166474752</v>
+        <v>3837452091392</v>
       </c>
       <c r="BO2" t="n">
         <v>0.24295999</v>
@@ -1565,31 +1585,31 @@
         <v>14840390000</v>
       </c>
       <c r="BR2" t="n">
-        <v>113582365</v>
+        <v>118199377</v>
       </c>
       <c r="BS2" t="n">
-        <v>104634941</v>
+        <v>127079143</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0077</v>
+        <v>0.008</v>
       </c>
       <c r="BW2" t="n">
         <v>0.0197</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.63641</v>
+        <v>0.63646</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0077</v>
+        <v>0.008</v>
       </c>
       <c r="CA2" t="n">
         <v>15318899712</v>
@@ -1598,7 +1618,7 @@
         <v>4.431</v>
       </c>
       <c r="CC2" t="n">
-        <v>56.779503</v>
+        <v>57.652897</v>
       </c>
       <c r="CD2" t="n">
         <v>1727481600</v>
@@ -1630,16 +1650,16 @@
         <v>1598832000</v>
       </c>
       <c r="CM2" t="n">
-        <v>9.353999999999999</v>
+        <v>9.391</v>
       </c>
       <c r="CN2" t="n">
-        <v>26.974</v>
+        <v>27.082</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.12395632</v>
+        <v>0.09639490000000001</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.26</v>
@@ -1653,7 +1673,7 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>251.59</v>
+        <v>255.46</v>
       </c>
       <c r="CU2" t="n">
         <v>310</v>
@@ -1662,7 +1682,7 @@
         <v>175</v>
       </c>
       <c r="CW2" t="n">
-        <v>242.31557</v>
+        <v>243.19057</v>
       </c>
       <c r="CX2" t="n">
         <v>243</v>
@@ -1775,172 +1795,184 @@
       </c>
       <c r="EC2" t="inlineStr">
         <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.548911</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>255.46</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.007824713000000001</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>255.48</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.019989014</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-1.40999</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>253.78 - 257.36</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>NasdaqGS</t>
+        </is>
+      </c>
+      <c r="EM2" t="n">
+        <v>56787322</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0.50972164</v>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>169.21 - 260.1</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-4.6399994</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.01783929</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>9.63949</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1755129600</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1753992000</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1761854400</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1761854400</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1753995600</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1753995600</v>
+      </c>
+      <c r="EZ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>7.38559</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>34.588978</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>27.0094</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>0.118228614</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>33.486404</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>0.1508576</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>2.0 - Buy</t>
+        </is>
+      </c>
+      <c r="FL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>345479400000</v>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="ED2" t="n">
-        <v>1758740007</v>
-      </c>
-      <c r="EE2" t="inlineStr">
+      <c r="FO2" t="n">
+        <v>1758931161</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>1758916800</v>
+      </c>
+      <c r="FQ2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="EF2" t="inlineStr">
+      <c r="FR2" t="inlineStr">
         <is>
           <t>finmb_24937</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="EI2" t="n">
+      <c r="FU2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="FV2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EK2" t="b">
+      <c r="FW2" t="b">
         <v>0</v>
       </c>
-      <c r="EL2" t="n">
-        <v>-1.1162192</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>251.59</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>7.38448</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>34.070103</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>25.84639</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0.11449445</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>29.79515</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>0.13433653</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EX2" t="n">
+      <c r="FX2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="FY2" t="b">
         <v>0</v>
       </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>2.0 - Buy</t>
-        </is>
-      </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>345479400000</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>-2.8399963</v>
-      </c>
-      <c r="FD2" t="inlineStr">
-        <is>
-          <t>251.04 - 255.73</t>
-        </is>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>NasdaqGS</t>
-        </is>
-      </c>
-      <c r="FF2" t="n">
-        <v>57103496</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>82.37999000000001</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>0.4868506</v>
-      </c>
-      <c r="FI2" t="inlineStr">
-        <is>
-          <t>169.21 - 260.1</t>
-        </is>
-      </c>
-      <c r="FJ2" t="n">
-        <v>-8.510009999999999</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>-0.032718223</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>12.395632</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>1755129600</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>1753992000</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>1761854400</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>1761854400</v>
-      </c>
-      <c r="FQ2" t="n">
-        <v>1753995600</v>
-      </c>
-      <c r="FR2" t="n">
-        <v>1753995600</v>
-      </c>
-      <c r="FS2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FT2" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="FU2" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="FV2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="FW2" t="n">
-        <v>2.4358</v>
+      <c r="GA2" t="n">
+        <v>2.4456</v>
       </c>
     </row>
   </sheetData>
